--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260916.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260916.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>137,855</t>
+          <t>138,255</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.19%</t>
+          <t>25.99%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>99,890</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>8.03%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>100,190</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.75%</t>
+          <t>7.94%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,815</t>
+          <t>50,915</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>121,125</t>
+          <t>121,425</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,610</t>
+          <t>59,910</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.64%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>18,283</t>
+          <t>18,383</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,355</t>
+          <t>65,455</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,725</t>
+          <t>19,825</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>76,945</t>
+          <t>77,245</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,245</t>
+          <t>20,345</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -968,95 +968,95 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>85,144,112</t>
+          <t>36,050</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,050</t>
+          <t>59,298</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>59,298</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>76,885,278</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>980,194</t>
+          <t>525,826</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RDI_USD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,530,100</t>
+          <t>31,024</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>-235,486</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
